--- a/GP2/Versuch_E17/Mitschriften_Versuch_E17.xlsx
+++ b/GP2/Versuch_E17/Mitschriften_Versuch_E17.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fynnlucca/Documents/Grundpraktikum-1/GP2/Versuch_E17/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1057C84-F0EE-F74B-A4FA-FA6D330E0427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C91B6736-E070-5C45-8799-2713DA160B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{D5C97754-4931-DE40-8915-B65B072F424C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
     <t>Versuch E17</t>
   </si>
@@ -78,6 +78,30 @@
   </si>
   <si>
     <t>dort sieht man immer f1 und f2, f2 aber stärker</t>
+  </si>
+  <si>
+    <t>2b</t>
+  </si>
+  <si>
+    <t>Kapazität gemessen 50nF</t>
+  </si>
+  <si>
+    <t>f1 = 1.817kHz</t>
+  </si>
+  <si>
+    <t>f2 = 1.392 kHz</t>
+  </si>
+  <si>
+    <t>Aufgabe 3</t>
+  </si>
+  <si>
+    <t>Spulenpaar 4</t>
+  </si>
+  <si>
+    <t>Ungekoppelt: f0 = 2.843 kHz</t>
+  </si>
+  <si>
+    <t>Abstand [cm]</t>
   </si>
 </sst>
 </file>
@@ -449,20 +473,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38F992DB-993D-B340-935A-C4889B48F88E}">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -472,8 +496,11 @@
       <c r="J6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="T6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -483,18 +510,38 @@
       <c r="J7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="T7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="T8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="J9" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="O9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="T10" t="s">
+        <v>21</v>
+      </c>
+      <c r="U10" t="s">
+        <v>8</v>
+      </c>
+      <c r="V10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>2</v>
       </c>
@@ -513,8 +560,20 @@
       <c r="L11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="O11" t="s">
+        <v>15</v>
+      </c>
+      <c r="T11">
+        <v>2.5</v>
+      </c>
+      <c r="U11">
+        <v>2.3780000000000001</v>
+      </c>
+      <c r="V11">
+        <v>3.7890000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10</v>
       </c>
@@ -533,8 +592,20 @@
       <c r="L12">
         <v>1.625</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="O12" t="s">
+        <v>16</v>
+      </c>
+      <c r="T12">
+        <v>4</v>
+      </c>
+      <c r="U12">
+        <v>2.496</v>
+      </c>
+      <c r="V12">
+        <v>3.4239999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>15</v>
       </c>
@@ -553,8 +624,20 @@
       <c r="L13">
         <v>1.62</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="O13" t="s">
+        <v>17</v>
+      </c>
+      <c r="T13">
+        <v>5</v>
+      </c>
+      <c r="U13">
+        <v>2.4780000000000002</v>
+      </c>
+      <c r="V13">
+        <v>3.4329999999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>20</v>
       </c>
@@ -573,8 +656,17 @@
       <c r="L14">
         <v>1.4830000000000001</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="T14">
+        <v>6.5</v>
+      </c>
+      <c r="U14">
+        <v>2.5870000000000002</v>
+      </c>
+      <c r="V14">
+        <v>3.214</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>35</v>
       </c>
@@ -593,8 +685,17 @@
       <c r="L15">
         <v>1.3919999999999999</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="T15">
+        <v>8</v>
+      </c>
+      <c r="U15">
+        <v>2.66</v>
+      </c>
+      <c r="V15">
+        <v>3.1040000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>50</v>
       </c>
@@ -613,8 +714,17 @@
       <c r="L16">
         <v>1.198</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="T16">
+        <v>9</v>
+      </c>
+      <c r="U16">
+        <v>2.6789999999999998</v>
+      </c>
+      <c r="V16">
+        <v>3.0489999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>100</v>
       </c>
@@ -633,8 +743,17 @@
       <c r="L17">
         <v>1.05</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="T17">
+        <v>11.5</v>
+      </c>
+      <c r="U17">
+        <v>2.7240000000000002</v>
+      </c>
+      <c r="V17">
+        <v>2.9670000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>200</v>
       </c>
@@ -653,8 +772,17 @@
       <c r="L18">
         <v>0.95799999999999996</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="T18">
+        <v>13</v>
+      </c>
+      <c r="U18">
+        <v>2.77</v>
+      </c>
+      <c r="V18">
+        <v>2.9220000000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>350</v>
       </c>
@@ -673,8 +801,17 @@
       <c r="L19">
         <v>0.76600000000000001</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="T19">
+        <v>14</v>
+      </c>
+      <c r="U19">
+        <v>2.77</v>
+      </c>
+      <c r="V19">
+        <v>2.903</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>500</v>
       </c>
@@ -693,8 +830,17 @@
       <c r="L20">
         <v>0.63890000000000002</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="T20">
+        <v>16.5</v>
+      </c>
+      <c r="U20">
+        <v>2.7709999999999999</v>
+      </c>
+      <c r="V20">
+        <v>2.907</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>1000</v>
       </c>
@@ -713,8 +859,17 @@
       <c r="L21">
         <v>0.47920000000000001</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="T21">
+        <v>17.5</v>
+      </c>
+      <c r="U21">
+        <v>2.8159999999999998</v>
+      </c>
+      <c r="V21">
+        <v>2.903</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>2000</v>
       </c>
@@ -724,8 +879,17 @@
       <c r="C22">
         <v>1.9419999999999999</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="T22">
+        <v>19</v>
+      </c>
+      <c r="U22">
+        <v>2.7949999999999999</v>
+      </c>
+      <c r="V22">
+        <v>2.907</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>5000</v>
       </c>
@@ -734,6 +898,15 @@
       </c>
       <c r="C23">
         <v>1.841</v>
+      </c>
+      <c r="T23">
+        <v>20</v>
+      </c>
+      <c r="U23">
+        <v>2.806</v>
+      </c>
+      <c r="V23">
+        <v>2.9129999999999998</v>
       </c>
     </row>
   </sheetData>

--- a/GP2/Versuch_E17/Mitschriften_Versuch_E17.xlsx
+++ b/GP2/Versuch_E17/Mitschriften_Versuch_E17.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fynnlucca/Documents/Grundpraktikum-1/GP2/Versuch_E17/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C91B6736-E070-5C45-8799-2713DA160B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEEF0EF4-B28C-3347-BD94-14B83EC1FF0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{D5C97754-4931-DE40-8915-B65B072F424C}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20400" xr2:uid="{D5C97754-4931-DE40-8915-B65B072F424C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -911,5 +911,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>